--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>58.4</v>
+        <v>64.2</v>
       </c>
       <c r="D2" t="n">
-        <v>59.87</v>
+        <v>64.2</v>
       </c>
       <c r="E2" t="n">
-        <v>57.03</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>67.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>64</v>
+        <v>63.27</v>
       </c>
       <c r="E3" t="n">
-        <v>61.67</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>64.2</v>
+        <v>66</v>
       </c>
       <c r="D4" t="n">
-        <v>64.2</v>
+        <v>63.2</v>
       </c>
       <c r="E4" t="n">
-        <v>62.37</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>65.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="D5" t="n">
-        <v>63.27</v>
+        <v>59.4</v>
       </c>
       <c r="E5" t="n">
-        <v>61.77</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D6" t="n">
-        <v>63.2</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>61.37</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>66.2</v>
+        <v>67.8</v>
       </c>
       <c r="D7" t="n">
-        <v>59.4</v>
+        <v>61.4</v>
       </c>
       <c r="E7" t="n">
-        <v>59.47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,61 +593,61 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>75</v>
+        <v>62.8</v>
       </c>
       <c r="D8" t="n">
-        <v>65.93000000000001</v>
+        <v>55.13</v>
       </c>
       <c r="E8" t="n">
-        <v>62.97</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>67.8</v>
+        <v>61.8</v>
       </c>
       <c r="D9" t="n">
-        <v>61.4</v>
+        <v>68.5</v>
       </c>
       <c r="E9" t="n">
-        <v>61</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>62.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>55.13</v>
+        <v>66.3</v>
       </c>
       <c r="E10" t="n">
-        <v>56.9</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>61.8</v>
+        <v>67.8</v>
       </c>
       <c r="D11" t="n">
-        <v>68.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>64.28</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>68.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>66.3</v>
+        <v>84.3</v>
       </c>
       <c r="E12" t="n">
-        <v>64.95999999999999</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>67.8</v>
+        <v>93.8</v>
       </c>
       <c r="D13" t="n">
-        <v>71.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="E13" t="n">
-        <v>67.28</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>89.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>84.3</v>
+        <v>82.2</v>
       </c>
       <c r="E14" t="n">
-        <v>74.16</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>93.8</v>
+        <v>92</v>
       </c>
       <c r="D15" t="n">
-        <v>88.8</v>
+        <v>87</v>
       </c>
       <c r="E15" t="n">
-        <v>78.04000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>83.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="D16" t="n">
-        <v>82.2</v>
+        <v>75.5</v>
       </c>
       <c r="E16" t="n">
-        <v>76.76000000000001</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>92</v>
+        <v>80.8</v>
       </c>
       <c r="D17" t="n">
-        <v>87</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>79</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>82</v>
+        <v>86.8</v>
       </c>
       <c r="D18" t="n">
-        <v>75.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>71.40000000000001</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>80.8</v>
+        <v>85</v>
       </c>
       <c r="D19" t="n">
-        <v>75.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E19" t="n">
-        <v>70.84</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>86.8</v>
+        <v>71</v>
       </c>
       <c r="D20" t="n">
-        <v>78.90000000000001</v>
+        <v>63</v>
       </c>
       <c r="E20" t="n">
-        <v>72.36</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>75.3</v>
+        <v>59.6</v>
       </c>
       <c r="E21" t="n">
-        <v>71.44</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>71</v>
+        <v>80.2</v>
       </c>
       <c r="D22" t="n">
-        <v>63</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>64.36</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>68.59999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="D23" t="n">
-        <v>59.6</v>
+        <v>58.6</v>
       </c>
       <c r="E23" t="n">
-        <v>60.52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>80.2</v>
+        <v>69.2</v>
       </c>
       <c r="D24" t="n">
-        <v>68.59999999999999</v>
+        <v>62.5</v>
       </c>
       <c r="E24" t="n">
-        <v>65.04000000000001</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>62.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>58.6</v>
+        <v>57.3</v>
       </c>
       <c r="E25" t="n">
-        <v>60</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,54 +971,12 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>69.2</v>
+        <v>52.2</v>
       </c>
       <c r="D26" t="n">
-        <v>62.5</v>
+        <v>47.3</v>
       </c>
       <c r="E26" t="n">
-        <v>61.88</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="D27" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="E27" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D28" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E28" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E2" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D3" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E3" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D4" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E4" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D5" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D6" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E6" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,40 +572,40 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D7" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D8" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E8" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E9" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D10" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E11" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D12" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E12" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E13" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E14" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E15" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D16" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D17" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D18" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E18" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D19" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E19" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E20" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D21" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D21" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E21" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D22" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E22" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D23" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E23" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E24" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,33 +950,12 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D25" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E25" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D26" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E26" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D2" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E2" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D3" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E3" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D4" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D5" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E5" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,40 +551,40 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D6" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D7" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E7" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E8" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D9" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E10" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D11" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E11" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E12" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E13" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E14" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D15" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D16" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D17" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E17" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D18" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E18" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E19" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D20" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D20" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E20" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D21" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E21" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D22" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E22" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E23" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,33 +929,12 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D24" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E24" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D25" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E25" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D2" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E2" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D3" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D4" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E4" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,40 +530,40 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D5" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E5" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D6" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E6" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E7" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D8" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E9" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D10" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E10" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E11" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E12" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E13" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D14" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D15" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D16" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E16" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E17" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E18" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D19" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D19" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E19" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D20" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E20" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D21" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E21" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E22" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,33 +908,12 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D23" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E23" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D24" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E24" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,82 +467,82 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>66.2</v>
+        <v>62.8</v>
       </c>
       <c r="D2" t="n">
-        <v>59.4</v>
+        <v>55.13</v>
       </c>
       <c r="E2" t="n">
-        <v>59.47</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>75</v>
+        <v>61.8</v>
       </c>
       <c r="D3" t="n">
-        <v>65.93000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="E3" t="n">
-        <v>62.97</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>67.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>61.4</v>
+        <v>66.3</v>
       </c>
       <c r="E4" t="n">
-        <v>61</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>62.8</v>
+        <v>67.8</v>
       </c>
       <c r="D5" t="n">
-        <v>55.13</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>56.9</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>61.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>68.5</v>
+        <v>84.3</v>
       </c>
       <c r="E6" t="n">
-        <v>64.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>68.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D7" t="n">
-        <v>66.3</v>
+        <v>88.8</v>
       </c>
       <c r="E7" t="n">
-        <v>64.95999999999999</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>67.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>71.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="E8" t="n">
-        <v>67.28</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>89.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D9" t="n">
-        <v>84.3</v>
+        <v>87</v>
       </c>
       <c r="E9" t="n">
-        <v>74.16</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>93.8</v>
+        <v>82</v>
       </c>
       <c r="D10" t="n">
-        <v>88.8</v>
+        <v>75.5</v>
       </c>
       <c r="E10" t="n">
-        <v>78.04000000000001</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>83.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="D11" t="n">
-        <v>82.2</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>76.76000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>86.8</v>
       </c>
       <c r="D12" t="n">
-        <v>87</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>79</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>75.5</v>
+        <v>75.3</v>
       </c>
       <c r="E13" t="n">
-        <v>71.40000000000001</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>80.8</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>75.40000000000001</v>
+        <v>63</v>
       </c>
       <c r="E14" t="n">
-        <v>70.84</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>86.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>78.90000000000001</v>
+        <v>59.6</v>
       </c>
       <c r="E15" t="n">
-        <v>72.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>85</v>
+        <v>80.2</v>
       </c>
       <c r="D16" t="n">
-        <v>75.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>71.44</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>62.8</v>
       </c>
       <c r="D17" t="n">
-        <v>63</v>
+        <v>58.6</v>
       </c>
       <c r="E17" t="n">
-        <v>64.36</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>68.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="D18" t="n">
-        <v>59.6</v>
+        <v>62.5</v>
       </c>
       <c r="E18" t="n">
-        <v>60.52</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>80.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>68.59999999999999</v>
+        <v>57.3</v>
       </c>
       <c r="E19" t="n">
-        <v>65.04000000000001</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,75 +845,12 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>62.8</v>
+        <v>52.2</v>
       </c>
       <c r="D20" t="n">
-        <v>58.6</v>
+        <v>47.3</v>
       </c>
       <c r="E20" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="D21" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="E21" t="n">
-        <v>61.88</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="D22" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="E22" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D23" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E23" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,28 +458,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D2" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E2" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E3" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D4" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E5" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D6" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E6" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E7" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D8" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E8" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D9" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E9" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D10" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D11" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E12" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D13" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E13" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E14" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D15" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D15" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E15" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D16" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E16" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D17" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E17" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E18" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,33 +824,12 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D19" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E19" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D20" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E20" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E2" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D3" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E4" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D5" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E5" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E6" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D7" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E7" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D8" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E8" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D9" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D10" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D11" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E11" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E12" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E13" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D14" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D14" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E14" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D15" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E15" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D16" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E16" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E17" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,33 +803,12 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D18" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E18" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D19" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E19" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D2" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E3" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D4" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E4" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E5" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D6" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D7" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E7" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D8" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D9" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D10" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E10" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D11" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E11" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E12" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D13" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D13" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E13" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D14" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E14" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D15" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E15" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E16" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,33 +782,12 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D17" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E17" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D18" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E18" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E2" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D3" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E3" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E4" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D5" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E5" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D6" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E6" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D7" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D8" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E9" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D10" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E10" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E11" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D12" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D12" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E12" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D13" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E13" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D14" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E14" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E15" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,33 +761,12 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D16" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E16" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E17" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D2" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E2" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E3" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D4" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E4" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E5" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D6" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D7" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D8" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E8" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D9" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E9" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E10" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D11" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D11" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E11" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D12" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E12" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D13" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E13" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E14" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,33 +740,12 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D15" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E15" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D16" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E16" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>93.8</v>
+        <v>92</v>
       </c>
       <c r="D2" t="n">
-        <v>88.8</v>
+        <v>87</v>
       </c>
       <c r="E2" t="n">
-        <v>78.04000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>83.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="D3" t="n">
-        <v>82.2</v>
+        <v>75.5</v>
       </c>
       <c r="E3" t="n">
-        <v>76.76000000000001</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>92</v>
+        <v>80.8</v>
       </c>
       <c r="D4" t="n">
-        <v>87</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>79</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>82</v>
+        <v>86.8</v>
       </c>
       <c r="D5" t="n">
-        <v>75.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>71.40000000000001</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>80.8</v>
+        <v>85</v>
       </c>
       <c r="D6" t="n">
-        <v>75.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E6" t="n">
-        <v>70.84</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>86.8</v>
+        <v>71</v>
       </c>
       <c r="D7" t="n">
-        <v>78.90000000000001</v>
+        <v>63</v>
       </c>
       <c r="E7" t="n">
-        <v>72.36</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>85</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>75.3</v>
+        <v>59.6</v>
       </c>
       <c r="E8" t="n">
-        <v>71.44</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>71</v>
+        <v>80.2</v>
       </c>
       <c r="D9" t="n">
-        <v>63</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>64.36</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>68.59999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="D10" t="n">
-        <v>59.6</v>
+        <v>58.6</v>
       </c>
       <c r="E10" t="n">
-        <v>60.52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>80.2</v>
+        <v>69.2</v>
       </c>
       <c r="D11" t="n">
-        <v>68.59999999999999</v>
+        <v>62.5</v>
       </c>
       <c r="E11" t="n">
-        <v>65.04000000000001</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>62.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>58.6</v>
+        <v>57.3</v>
       </c>
       <c r="E12" t="n">
-        <v>60</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,54 +698,12 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>69.2</v>
+        <v>52.2</v>
       </c>
       <c r="D13" t="n">
-        <v>62.5</v>
+        <v>47.3</v>
       </c>
       <c r="E13" t="n">
-        <v>61.88</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="D14" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="E14" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D15" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E15" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D2" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E2" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D3" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D4" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D5" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E5" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D6" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E6" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E7" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D8" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D8" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E8" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D9" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E9" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D10" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E10" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E11" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,33 +677,12 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D12" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E12" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E13" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D2" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D3" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D4" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E4" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D5" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E5" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E6" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D7" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D7" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E7" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D8" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E8" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D9" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E10" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,33 +656,12 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D11" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E11" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D12" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E12" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D2" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D3" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E3" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D4" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E4" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E5" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D6" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D6" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E6" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D7" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E7" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D8" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E9" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,33 +635,12 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D10" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E10" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D11" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E11" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>86.8</v>
+        <v>71</v>
       </c>
       <c r="D2" t="n">
-        <v>78.90000000000001</v>
+        <v>63</v>
       </c>
       <c r="E2" t="n">
-        <v>72.36</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>85</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>75.3</v>
+        <v>59.6</v>
       </c>
       <c r="E3" t="n">
-        <v>71.44</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>71</v>
+        <v>80.2</v>
       </c>
       <c r="D4" t="n">
-        <v>63</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>64.36</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>68.59999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="D5" t="n">
-        <v>59.6</v>
+        <v>58.6</v>
       </c>
       <c r="E5" t="n">
-        <v>60.52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>80.2</v>
+        <v>69.2</v>
       </c>
       <c r="D6" t="n">
-        <v>68.59999999999999</v>
+        <v>62.5</v>
       </c>
       <c r="E6" t="n">
-        <v>65.04000000000001</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>62.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>58.6</v>
+        <v>57.3</v>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,54 +593,12 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>69.2</v>
+        <v>52.2</v>
       </c>
       <c r="D8" t="n">
-        <v>62.5</v>
+        <v>47.3</v>
       </c>
       <c r="E8" t="n">
-        <v>61.88</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="D9" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="E9" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D10" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E10" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E2" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D3" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D3" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E3" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D4" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E4" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D5" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E5" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E6" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,33 +572,12 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D7" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E7" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D8" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E8" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D2" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D2" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E2" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D3" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E3" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D4" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E4" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E5" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,33 +551,12 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D6" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E6" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D7" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E7" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D2" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E2" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D3" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E4" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,33 +530,12 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D5" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E5" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E6" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>62.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>58.6</v>
+        <v>57.3</v>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,54 +488,12 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>69.2</v>
+        <v>52.2</v>
       </c>
       <c r="D3" t="n">
-        <v>62.5</v>
+        <v>47.3</v>
       </c>
       <c r="E3" t="n">
-        <v>61.88</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="D4" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="E4" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E5" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,33 +467,12 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D2" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E2" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E3" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,31 +413,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>当月合约</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>当月-下月/月差</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>当月-当季/月差</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>当月-下季/月差</t>
         </is>
@@ -458,22 +446,1093 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IC2607</t>
+          <t>IC2601</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>52.2</v>
+        <v>42.6</v>
       </c>
       <c r="D2" t="n">
-        <v>47.3</v>
+        <v>42.5</v>
       </c>
       <c r="E2" t="n">
-        <v>54.08</v>
+        <v>52.8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>IC2601</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="D3" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>51.24</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>IC2601</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>56.04</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>IC2601</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>40</v>
+      </c>
+      <c r="D5" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>49.56</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>IC2601</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>44.52</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>IC2601</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IC2601</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>49.68</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>IC2601</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D9" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>44.52</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>IC2601</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>38.08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>IC2601</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>37.52</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>IC2601</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>36.44</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>IC2601</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IC2602</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="D14" t="n">
+        <v>33.45</v>
+      </c>
+      <c r="E14" t="n">
+        <v>36.83</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>IC2602</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>9</v>
+      </c>
+      <c r="D15" t="n">
+        <v>28.95</v>
+      </c>
+      <c r="E15" t="n">
+        <v>33.37</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>IC2602</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="E16" t="n">
+        <v>30.74</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>IC2602</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>29.83</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>IC2602</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="E18" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>IC2602</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="E19" t="n">
+        <v>32.14</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>IC2602</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="E20" t="n">
+        <v>26.26</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>IC2602</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>22.03</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>IC2602</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="D22" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="E22" t="n">
+        <v>22.46</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>IC2602</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="D23" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>23.89</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>IC2602</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="D24" t="n">
+        <v>46.45</v>
+      </c>
+      <c r="E24" t="n">
+        <v>43.43</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>IC2602</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="E25" t="n">
+        <v>28.69</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>IC2602</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="E26" t="n">
+        <v>30.86</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>IC2602</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="D27" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>34.97</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>IC2602</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="E28" t="n">
+        <v>34.37</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>IC2602</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="D29" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E29" t="n">
+        <v>32.4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>IC2602</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>29.95</v>
+      </c>
+      <c r="E30" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>IC2602</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E31" t="n">
+        <v>32.14</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>IC2602</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="D32" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="E32" t="n">
+        <v>30.51</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>IC2602</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="D33" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>33.54</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>IC2603</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>30.53</v>
+      </c>
+      <c r="E34" t="n">
+        <v>35.33</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>IC2603</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="D35" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="E35" t="n">
+        <v>39.87</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>IC2603</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>40.07</v>
+      </c>
+      <c r="E36" t="n">
+        <v>44.87</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>IC2603</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>24</v>
+      </c>
+      <c r="D37" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="E37" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>IC2603</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="D38" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="E38" t="n">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>IC2603</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="D39" t="n">
+        <v>47.87</v>
+      </c>
+      <c r="E39" t="n">
+        <v>49.63</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>IC2603</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="D40" t="n">
+        <v>56</v>
+      </c>
+      <c r="E40" t="n">
+        <v>55.67</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>IC2603</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="D41" t="n">
+        <v>57.27</v>
+      </c>
+      <c r="E41" t="n">
+        <v>57.47</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>IC2603</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>47</v>
+      </c>
+      <c r="D42" t="n">
+        <v>61.73</v>
+      </c>
+      <c r="E42" t="n">
+        <v>60.87</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>IC2603</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="D43" t="n">
+        <v>51.53</v>
+      </c>
+      <c r="E43" t="n">
+        <v>51.73</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>IC2603</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="D44" t="n">
+        <v>53.53</v>
+      </c>
+      <c r="E44" t="n">
+        <v>53.6</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>IC2603</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="D45" t="n">
+        <v>57.93</v>
+      </c>
+      <c r="E45" t="n">
+        <v>55.2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>IC2603</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="D46" t="n">
+        <v>61</v>
+      </c>
+      <c r="E46" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>IC2603</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="D47" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="E47" t="n">
+        <v>56.6</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>IC2603</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>50</v>
+      </c>
+      <c r="D48" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="E48" t="n">
+        <v>61.3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>IC2603</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>55</v>
+      </c>
+      <c r="D49" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="E49" t="n">
+        <v>61.97</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>IC2603</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="D50" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="E50" t="n">
+        <v>65.37</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>IC2604</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>50</v>
+      </c>
+      <c r="D51" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="E51" t="n">
+        <v>67.72</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>IC2604</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="D52" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="E52" t="n">
+        <v>63.08</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>IC2604</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="D53" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="E53" t="n">
+        <v>66.12</v>
       </c>
     </row>
   </sheetData>
